--- a/excel/denial-prevention-simulator_dashboard.xlsx
+++ b/excel/denial-prevention-simulator_dashboard.xlsx
@@ -348,6 +348,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_controls'!$A$2:$A$6</f>
@@ -413,6 +414,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -441,6 +443,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <valAx>
         <axId val="200"/>
@@ -560,6 +563,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_by_service'!$A$2:$A$10</f>
@@ -584,6 +588,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -611,6 +616,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <valAx>
         <axId val="200"/>
@@ -690,6 +696,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_risk_band'!$A$2:$A$4</f>
@@ -714,6 +721,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -742,6 +750,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -790,6 +799,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_submit_lag'!$A$2:$A$6</f>
@@ -814,6 +824,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -842,6 +853,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -931,6 +943,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_monthly'!$A$2:$A$9</f>
@@ -955,6 +968,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -982,6 +996,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <valAx>
         <axId val="200"/>
@@ -1061,6 +1076,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_resub'!$A$2:$A$3</f>
@@ -1089,6 +1105,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_resub'!$A$2:$A$3</f>
@@ -1113,6 +1130,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -1126,6 +1144,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
     </plotArea>
     <legend>
@@ -1178,6 +1197,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'q_queue_owner'!$A$2:$A$7</f>
@@ -1243,6 +1263,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="100"/>
+        <crosses val="autoZero"/>
         <lblOffset val="100"/>
       </catAx>
       <valAx>
@@ -1271,6 +1292,7 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+        <crosses val="autoZero"/>
       </valAx>
       <valAx>
         <axId val="200"/>
